--- a/fixtures/legacy/old-app-sections.xlsx
+++ b/fixtures/legacy/old-app-sections.xlsx
@@ -91,10 +91,10 @@
     <t>Full</t>
   </si>
   <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>101</t>
+    <t>MUSC</t>
+  </si>
+  <si>
+    <t>104</t>
   </si>
   <si>
     <t>A</t>
@@ -115,7 +115,7 @@
     <t>NH 101</t>
   </si>
   <si>
-    <t>Calculus I</t>
+    <t>Musical Patterns I</t>
   </si>
   <si>
     <t>Lecture</t>
@@ -130,7 +130,7 @@
     <t>10:30:00</t>
   </si>
   <si>
-    <t>102</t>
+    <t>105</t>
   </si>
   <si>
     <t>Ben Sample</t>
@@ -142,10 +142,10 @@
     <t>NH 102</t>
   </si>
   <si>
-    <t>Calculus II</t>
-  </si>
-  <si>
-    <t>231</t>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>234</t>
   </si>
   <si>
     <t>Cy Fictional</t>
@@ -160,22 +160,22 @@
     <t>NH 103</t>
   </si>
   <si>
-    <t>Linear Algebra</t>
+    <t>Harmonic Structures</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>250</t>
+    <t>253</t>
   </si>
   <si>
     <t>08:00:00</t>
   </si>
   <si>
-    <t>Discrete Mathematics</t>
-  </si>
-  <si>
-    <t>301</t>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>304</t>
   </si>
   <si>
     <t>14:10:00</t>
@@ -184,13 +184,13 @@
     <t>NH 104</t>
   </si>
   <si>
-    <t>Real Analysis I</t>
+    <t>Corpus Studies I</t>
   </si>
   <si>
     <t>300</t>
   </si>
   <si>
-    <t>391</t>
+    <t>394</t>
   </si>
   <si>
     <t>R</t>
@@ -211,10 +211,10 @@
     <t>Seminar</t>
   </si>
   <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>143</t>
+    <t>URBS</t>
+  </si>
+  <si>
+    <t>146</t>
   </si>
   <si>
     <t>Dee Placeholder</t>
@@ -226,7 +226,7 @@
     <t>NH 105</t>
   </si>
   <si>
-    <t>Introduction to Statistics</t>
+    <t>Introduction to Behavioral Dynamics</t>
   </si>
   <si>
     <t xml:space="preserve">MWF
@@ -245,16 +245,16 @@
 NH 106</t>
   </si>
   <si>
-    <t>243</t>
+    <t>246</t>
   </si>
   <si>
     <t>Eli Specimen</t>
   </si>
   <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>343</t>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>346</t>
   </si>
   <si>
     <t>Eli Specimen, Dee Placeholder</t>
@@ -276,13 +276,13 @@
 NH 105</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>202</t>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>205</t>
   </si>
   <si>
     <t>Fay Mockson</t>
@@ -294,16 +294,16 @@
     <t>SB 110</t>
   </si>
   <si>
-    <t>Data Computing</t>
+    <t>Information Computing</t>
   </si>
   <si>
     <t>Computer Science</t>
   </si>
   <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>108</t>
+    <t>CRUD</t>
+  </si>
+  <si>
+    <t>111</t>
   </si>
   <si>
     <t>Gus Testwell</t>
@@ -312,10 +312,10 @@
     <t>SB 120</t>
   </si>
   <si>
-    <t>Introduction to Computing</t>
-  </si>
-  <si>
-    <t>262</t>
+    <t>Introduction to Urban Systems</t>
+  </si>
+  <si>
+    <t>265</t>
   </si>
   <si>
     <t>Hal Fakename</t>
@@ -327,16 +327,16 @@
     <t>SB 122</t>
   </si>
   <si>
-    <t>Data Structures</t>
+    <t>Urban Data Structures</t>
   </si>
   <si>
     <t>Student Success</t>
   </si>
   <si>
-    <t>ASC</t>
-  </si>
-  <si>
-    <t>111</t>
+    <t>AMUS</t>
+  </si>
+  <si>
+    <t>114</t>
   </si>
   <si>
     <t>Ivy Sandbox</t>
@@ -345,7 +345,7 @@
     <t>HH 316</t>
   </si>
   <si>
-    <t>Academic Transitions</t>
+    <t>Transitions in Ecology</t>
   </si>
   <si>
     <t xml:space="preserve">12:15:00
@@ -371,25 +371,25 @@
     <t>SP</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>Multivariable Calculus</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>Real Analysis II</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression Models</t>
-  </si>
-  <si>
-    <t>344</t>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>347</t>
   </si>
   <si>
     <t>Bayesian Statistics</t>
@@ -401,16 +401,16 @@
     <t>MW</t>
   </si>
   <si>
-    <t>Data Science Topics</t>
-  </si>
-  <si>
-    <t>372</t>
+    <t>Digital Information Topics</t>
+  </si>
+  <si>
+    <t>375</t>
   </si>
   <si>
     <t>13:30:00</t>
   </si>
   <si>
-    <t>Algorithms</t>
+    <t>Planning Algorithms</t>
   </si>
 </sst>
 </file>
